--- a/research/traditional_assets/database/data/norway/norway_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.198</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E2">
-        <v>0.349</v>
+        <v>0.0866</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,91 +606,91 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>91.90000000000001</v>
+        <v>34.9</v>
       </c>
       <c r="L2">
-        <v>0.2710115010321439</v>
+        <v>0.1946458449525934</v>
       </c>
       <c r="M2">
-        <v>21</v>
+        <v>45.53</v>
       </c>
       <c r="N2">
-        <v>0.04337050805452292</v>
+        <v>0.1670825688073395</v>
       </c>
       <c r="O2">
-        <v>0.2285092491838955</v>
+        <v>1.30458452722063</v>
       </c>
       <c r="P2">
-        <v>21</v>
+        <v>43.6</v>
       </c>
       <c r="Q2">
-        <v>0.04337050805452292</v>
+        <v>0.16</v>
       </c>
       <c r="R2">
-        <v>0.2285092491838955</v>
+        <v>1.249283667621777</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.04238963320887326</v>
       </c>
       <c r="U2">
-        <v>143.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="V2">
-        <v>0.2957455596860801</v>
+        <v>0.3115596330275229</v>
       </c>
       <c r="W2">
-        <v>1.185806451612903</v>
+        <v>0.2930310663308144</v>
       </c>
       <c r="X2">
-        <v>0.0340513878133225</v>
+        <v>0.0695307864536968</v>
       </c>
       <c r="Y2">
-        <v>1.151755063799581</v>
+        <v>0.2235002798771176</v>
       </c>
       <c r="Z2">
-        <v>16.14761904761905</v>
+        <v>64.03571428571404</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03321762887066314</v>
+        <v>0.06460831694805977</v>
       </c>
       <c r="AC2">
-        <v>-0.03321762887066314</v>
+        <v>-0.06460831694805977</v>
       </c>
       <c r="AD2">
-        <v>26.9</v>
+        <v>48.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>26.9</v>
+        <v>48.4</v>
       </c>
       <c r="AG2">
-        <v>-116.3</v>
+        <v>-36.50000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.05263157894736843</v>
+        <v>0.1508258024306638</v>
       </c>
       <c r="AI2">
-        <v>0.1824966078697422</v>
+        <v>0.3595839524517088</v>
       </c>
       <c r="AJ2">
-        <v>-0.3161185104648002</v>
+        <v>-0.1546610169491526</v>
       </c>
       <c r="AK2">
-        <v>-27.69047619047607</v>
+        <v>-0.734406438631791</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-3.85</v>
+        <v>-2.93</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.198</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E3">
-        <v>0.349</v>
+        <v>0.0866</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,91 +731,91 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>91.90000000000001</v>
+        <v>34.9</v>
       </c>
       <c r="L3">
-        <v>0.2710115010321439</v>
+        <v>0.1946458449525934</v>
       </c>
       <c r="M3">
-        <v>21</v>
+        <v>45.53</v>
       </c>
       <c r="N3">
-        <v>0.04337050805452292</v>
+        <v>0.1670825688073395</v>
       </c>
       <c r="O3">
-        <v>0.2285092491838955</v>
+        <v>1.30458452722063</v>
       </c>
       <c r="P3">
-        <v>21</v>
+        <v>43.6</v>
       </c>
       <c r="Q3">
-        <v>0.04337050805452292</v>
+        <v>0.16</v>
       </c>
       <c r="R3">
-        <v>0.2285092491838955</v>
+        <v>1.249283667621777</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.04238963320887326</v>
       </c>
       <c r="U3">
-        <v>143.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="V3">
-        <v>0.2957455596860801</v>
+        <v>0.3115596330275229</v>
       </c>
       <c r="W3">
-        <v>1.185806451612903</v>
+        <v>0.2930310663308144</v>
       </c>
       <c r="X3">
-        <v>0.0340513878133225</v>
+        <v>0.0695307864536968</v>
       </c>
       <c r="Y3">
-        <v>1.151755063799581</v>
+        <v>0.2235002798771176</v>
       </c>
       <c r="Z3">
-        <v>16.14761904761905</v>
+        <v>64.03571428571404</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03321762887066314</v>
+        <v>0.06460831694805977</v>
       </c>
       <c r="AC3">
-        <v>-0.03321762887066314</v>
+        <v>-0.06460831694805977</v>
       </c>
       <c r="AD3">
-        <v>26.9</v>
+        <v>48.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>26.9</v>
+        <v>48.4</v>
       </c>
       <c r="AG3">
-        <v>-116.3</v>
+        <v>-36.50000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.05263157894736843</v>
+        <v>0.1508258024306638</v>
       </c>
       <c r="AI3">
-        <v>0.1824966078697422</v>
+        <v>0.3595839524517088</v>
       </c>
       <c r="AJ3">
-        <v>-0.3161185104648002</v>
+        <v>-0.1546610169491526</v>
       </c>
       <c r="AK3">
-        <v>-27.69047619047607</v>
+        <v>-0.734406438631791</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-3.85</v>
+        <v>-2.93</v>
       </c>
       <c r="AQ3">
         <v>-0</v>

--- a/research/traditional_assets/database/data/norway/norway_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08699999999999999</v>
+        <v>0.0576</v>
       </c>
       <c r="E2">
-        <v>0.0866</v>
+        <v>0.029</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,91 +606,91 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>34.9</v>
+        <v>21.6</v>
       </c>
       <c r="L2">
-        <v>0.1946458449525934</v>
+        <v>0.1421988150098749</v>
       </c>
       <c r="M2">
-        <v>45.53</v>
+        <v>49.54</v>
       </c>
       <c r="N2">
-        <v>0.1670825688073395</v>
+        <v>0.1514058679706602</v>
       </c>
       <c r="O2">
-        <v>1.30458452722063</v>
+        <v>2.293518518518519</v>
       </c>
       <c r="P2">
-        <v>43.6</v>
+        <v>44.1</v>
       </c>
       <c r="Q2">
-        <v>0.16</v>
+        <v>0.1347799511002445</v>
       </c>
       <c r="R2">
-        <v>1.249283667621777</v>
+        <v>2.041666666666667</v>
       </c>
       <c r="S2">
-        <v>1.93</v>
+        <v>5.439999999999998</v>
       </c>
       <c r="T2">
-        <v>0.04238963320887326</v>
+        <v>0.1098102543399273</v>
       </c>
       <c r="U2">
-        <v>84.90000000000001</v>
+        <v>58.1</v>
       </c>
       <c r="V2">
-        <v>0.3115596330275229</v>
+        <v>0.1775672371638142</v>
       </c>
       <c r="W2">
-        <v>0.2930310663308144</v>
+        <v>0.2514551804423749</v>
       </c>
       <c r="X2">
-        <v>0.0695307864536968</v>
+        <v>0.05983896924846881</v>
       </c>
       <c r="Y2">
-        <v>0.2235002798771176</v>
+        <v>0.191616211193906</v>
       </c>
       <c r="Z2">
-        <v>64.03571428571404</v>
+        <v>3.074898785425101</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06460831694805977</v>
+        <v>0.05517722075898586</v>
       </c>
       <c r="AC2">
-        <v>-0.06460831694805977</v>
+        <v>-0.05517722075898586</v>
       </c>
       <c r="AD2">
-        <v>48.4</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>48.4</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AG2">
-        <v>-36.50000000000001</v>
+        <v>17.99999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.1508258024306638</v>
+        <v>0.1886932804363997</v>
       </c>
       <c r="AI2">
-        <v>0.3595839524517088</v>
+        <v>0.4822560202788339</v>
       </c>
       <c r="AJ2">
-        <v>-0.1546610169491526</v>
+        <v>0.05214368482039396</v>
       </c>
       <c r="AK2">
-        <v>-0.734406438631791</v>
+        <v>0.1805416248746238</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-2.93</v>
+        <v>-5.2</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08699999999999999</v>
+        <v>0.0576</v>
       </c>
       <c r="E3">
-        <v>0.0866</v>
+        <v>0.029</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,91 +731,91 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>34.9</v>
+        <v>21.6</v>
       </c>
       <c r="L3">
-        <v>0.1946458449525934</v>
+        <v>0.1421988150098749</v>
       </c>
       <c r="M3">
-        <v>45.53</v>
+        <v>49.54</v>
       </c>
       <c r="N3">
-        <v>0.1670825688073395</v>
+        <v>0.1514058679706602</v>
       </c>
       <c r="O3">
-        <v>1.30458452722063</v>
+        <v>2.293518518518519</v>
       </c>
       <c r="P3">
-        <v>43.6</v>
+        <v>44.1</v>
       </c>
       <c r="Q3">
-        <v>0.16</v>
+        <v>0.1347799511002445</v>
       </c>
       <c r="R3">
-        <v>1.249283667621777</v>
+        <v>2.041666666666667</v>
       </c>
       <c r="S3">
-        <v>1.93</v>
+        <v>5.439999999999998</v>
       </c>
       <c r="T3">
-        <v>0.04238963320887326</v>
+        <v>0.1098102543399273</v>
       </c>
       <c r="U3">
-        <v>84.90000000000001</v>
+        <v>58.1</v>
       </c>
       <c r="V3">
-        <v>0.3115596330275229</v>
+        <v>0.1775672371638142</v>
       </c>
       <c r="W3">
-        <v>0.2930310663308144</v>
+        <v>0.2514551804423749</v>
       </c>
       <c r="X3">
-        <v>0.0695307864536968</v>
+        <v>0.05983896924846881</v>
       </c>
       <c r="Y3">
-        <v>0.2235002798771176</v>
+        <v>0.191616211193906</v>
       </c>
       <c r="Z3">
-        <v>64.03571428571404</v>
+        <v>3.074898785425101</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06460831694805977</v>
+        <v>0.05517722075898586</v>
       </c>
       <c r="AC3">
-        <v>-0.06460831694805977</v>
+        <v>-0.05517722075898586</v>
       </c>
       <c r="AD3">
-        <v>48.4</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>48.4</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>-36.50000000000001</v>
+        <v>17.99999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.1508258024306638</v>
+        <v>0.1886932804363997</v>
       </c>
       <c r="AI3">
-        <v>0.3595839524517088</v>
+        <v>0.4822560202788339</v>
       </c>
       <c r="AJ3">
-        <v>-0.1546610169491526</v>
+        <v>0.05214368482039396</v>
       </c>
       <c r="AK3">
-        <v>-0.734406438631791</v>
+        <v>0.1805416248746238</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-2.93</v>
+        <v>-5.2</v>
       </c>
       <c r="AQ3">
         <v>-0</v>
